--- a/grc_wisdom_api/scripts/verify/_tmp/Issue_register.xlsx
+++ b/grc_wisdom_api/scripts/verify/_tmp/Issue_register.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="88" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="88" uniqueCount="60">
   <si>
     <t>Issue Register</t>
   </si>
@@ -35,7 +35,7 @@
     <t>Generated at</t>
   </si>
   <si>
-    <t>2026-09-23 10:59 UTC</t>
+    <t>2026-09-24 22:36 UTC</t>
   </si>
   <si>
     <t>Visibility</t>
@@ -47,7 +47,7 @@
     <t>Document reference</t>
   </si>
   <si>
-    <t>1172-20260923105942</t>
+    <t>97EF-20260924223621</t>
   </si>
   <si>
     <t>Ref</t>
@@ -116,40 +116,40 @@
     <t>CAPAssigned</t>
   </si>
   <si>
+    <t>Noura Alsuhaimi</t>
+  </si>
+  <si>
+    <t>Mehdi Tantaoui</t>
+  </si>
+  <si>
+    <t>2026-08-08</t>
+  </si>
+  <si>
+    <t>2026-10-07</t>
+  </si>
+  <si>
+    <t>47</t>
+  </si>
+  <si>
+    <t>AUD-2026-02-F1</t>
+  </si>
+  <si>
+    <t>AUD-2026-02</t>
+  </si>
+  <si>
+    <t>Three activities in the marketing workspace lack a recorded basis.</t>
+  </si>
+  <si>
+    <t>High</t>
+  </si>
+  <si>
     <t>Abdullah Alfifi</t>
   </si>
   <si>
-    <t>Shahd Hamdan</t>
-  </si>
-  <si>
-    <t>2026-08-07</t>
-  </si>
-  <si>
-    <t>2026-10-06</t>
-  </si>
-  <si>
-    <t>47</t>
-  </si>
-  <si>
-    <t>AUD-2026-02-F1</t>
-  </si>
-  <si>
-    <t>AUD-2026-02</t>
-  </si>
-  <si>
-    <t>Three activities in the marketing workspace lack a recorded basis.</t>
-  </si>
-  <si>
-    <t>High</t>
-  </si>
-  <si>
-    <t>Ibrahim Abdulaziz</t>
-  </si>
-  <si>
-    <t>2026-08-19</t>
-  </si>
-  <si>
-    <t>2026-09-18</t>
+    <t>2026-08-20</t>
+  </si>
+  <si>
+    <t>2026-09-19</t>
   </si>
   <si>
     <t>35</t>
@@ -176,16 +176,19 @@
     <t>RCSA-2026-01</t>
   </si>
   <si>
-    <t>Self-assessed ineffective control: AC-03</t>
+    <t>Self-assessed ineffective control: PDP-03</t>
   </si>
   <si>
     <t>Open</t>
   </si>
   <si>
-    <t>2026-09-15</t>
-  </si>
-  <si>
-    <t>2026-11-14</t>
+    <t>Hassan Rahman</t>
+  </si>
+  <si>
+    <t>2026-09-16</t>
+  </si>
+  <si>
+    <t>2026-11-15</t>
   </si>
   <si>
     <t>8</t>
@@ -934,19 +937,19 @@
         <v>55</v>
       </c>
       <c r="I5" s="9" t="s">
-        <v>35</v>
+        <v>56</v>
       </c>
       <c r="J5" s="9" t="s">
         <v>29</v>
       </c>
       <c r="K5" s="9" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="L5" s="9" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="M5" s="9" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="N5" s="9" t="s">
         <v>29</v>
